--- a/Data/EXCEL/Transfer/salemon/202208/6575-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6575-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4021D881-7C5C-48C6-89A4-1C777C2D23A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F204BC4-24A4-41FD-A831-ED102DCD185E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6575-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -261,9 +261,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,14 +1226,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="5" width="11.25" customWidth="1"/>
-    <col min="6" max="7" width="10.75" customWidth="1"/>
-    <col min="8" max="16" width="9.375" customWidth="1"/>
-    <col min="17" max="17" width="10.125" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="15.25" customWidth="1"/>
+    <col min="8" max="16" width="13.25" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1378,25 +1386,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="C5" s="7">
-        <v>71.8</v>
+        <v>52.6</v>
       </c>
       <c r="D5" s="7">
-        <v>73.2</v>
+        <v>80</v>
       </c>
       <c r="E5" s="7">
-        <v>59</v>
+        <v>46.55</v>
       </c>
       <c r="F5" s="8">
-        <v>0.6</v>
+        <v>-19.2</v>
       </c>
       <c r="G5" s="8">
-        <v>0.84</v>
+        <v>-26.74</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1431,25 +1439,25 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>72.3</v>
+        <v>71.2</v>
       </c>
       <c r="C6" s="7">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="D6" s="7">
-        <v>74.8</v>
+        <v>73.2</v>
       </c>
       <c r="E6" s="7">
-        <v>67.2</v>
+        <v>59</v>
       </c>
       <c r="F6" s="10">
-        <v>-1.1000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="10">
-        <v>-1.52</v>
+        <v>0.84</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1484,25 +1492,25 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>75.400000000000006</v>
+        <v>72.3</v>
       </c>
       <c r="C7" s="7">
-        <v>72.3</v>
+        <v>71.2</v>
       </c>
       <c r="D7" s="7">
-        <v>77.900000000000006</v>
+        <v>74.8</v>
       </c>
       <c r="E7" s="7">
-        <v>66.8</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-3.1</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-4.1100000000000003</v>
+        <v>67.2</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-1.52</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1537,25 +1545,25 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>66.5</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="C8" s="7">
-        <v>75.400000000000006</v>
+        <v>72.3</v>
       </c>
       <c r="D8" s="7">
-        <v>90</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="E8" s="7">
-        <v>64.099999999999994</v>
+        <v>66.8</v>
       </c>
       <c r="F8" s="8">
-        <v>8.9</v>
+        <v>-3.1</v>
       </c>
       <c r="G8" s="8">
-        <v>13.38</v>
+        <v>-4.1100000000000003</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1590,25 +1598,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>65.099999999999994</v>
+        <v>66.5</v>
       </c>
       <c r="C9" s="7">
-        <v>66.5</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="D9" s="7">
-        <v>68.7</v>
+        <v>90</v>
       </c>
       <c r="E9" s="7">
-        <v>56.3</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1.4</v>
-      </c>
-      <c r="G9" s="8">
-        <v>2.15</v>
+        <v>64.099999999999994</v>
+      </c>
+      <c r="F9" s="10">
+        <v>8.9</v>
+      </c>
+      <c r="G9" s="10">
+        <v>13.38</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1643,25 +1651,25 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>56.5</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="C10" s="7">
-        <v>65.099999999999994</v>
+        <v>66.5</v>
       </c>
       <c r="D10" s="7">
-        <v>72</v>
+        <v>68.7</v>
       </c>
       <c r="E10" s="7">
-        <v>56</v>
-      </c>
-      <c r="F10" s="8">
-        <v>8.6</v>
-      </c>
-      <c r="G10" s="8">
-        <v>15.22</v>
+        <v>56.3</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="G10" s="10">
+        <v>2.15</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1696,25 +1704,25 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>49.1</v>
+        <v>56.5</v>
       </c>
       <c r="C11" s="7">
-        <v>56.5</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="D11" s="7">
-        <v>79.3</v>
+        <v>72</v>
       </c>
       <c r="E11" s="7">
-        <v>48.45</v>
-      </c>
-      <c r="F11" s="8">
-        <v>7.4</v>
-      </c>
-      <c r="G11" s="8">
-        <v>15.07</v>
+        <v>56</v>
+      </c>
+      <c r="F11" s="10">
+        <v>8.6</v>
+      </c>
+      <c r="G11" s="10">
+        <v>15.22</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1749,25 +1757,25 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>47.75</v>
+        <v>49.1</v>
       </c>
       <c r="C12" s="7">
-        <v>49.1</v>
+        <v>56.5</v>
       </c>
       <c r="D12" s="7">
-        <v>53.4</v>
+        <v>79.3</v>
       </c>
       <c r="E12" s="7">
-        <v>46.7</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1.35</v>
-      </c>
-      <c r="G12" s="8">
-        <v>2.83</v>
+        <v>48.45</v>
+      </c>
+      <c r="F12" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="G12" s="10">
+        <v>15.07</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -1802,25 +1810,25 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>45.65</v>
+        <v>47.75</v>
       </c>
       <c r="C13" s="7">
-        <v>47.75</v>
+        <v>49.1</v>
       </c>
       <c r="D13" s="7">
-        <v>48.4</v>
+        <v>53.4</v>
       </c>
       <c r="E13" s="7">
-        <v>42.05</v>
-      </c>
-      <c r="F13" s="8">
-        <v>2.1</v>
-      </c>
-      <c r="G13" s="8">
-        <v>4.5999999999999996</v>
+        <v>46.7</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1.35</v>
+      </c>
+      <c r="G13" s="10">
+        <v>2.83</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -1855,25 +1863,25 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>47.35</v>
+        <v>45.65</v>
       </c>
       <c r="C14" s="7">
-        <v>45.65</v>
+        <v>47.75</v>
       </c>
       <c r="D14" s="7">
-        <v>50.4</v>
+        <v>48.4</v>
       </c>
       <c r="E14" s="7">
-        <v>44.85</v>
+        <v>42.05</v>
       </c>
       <c r="F14" s="10">
-        <v>-1.7</v>
+        <v>2.1</v>
       </c>
       <c r="G14" s="10">
-        <v>-3.59</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1908,25 +1916,25 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>48.5</v>
+        <v>47.35</v>
       </c>
       <c r="C15" s="7">
-        <v>47.35</v>
+        <v>45.65</v>
       </c>
       <c r="D15" s="7">
-        <v>53.4</v>
+        <v>50.4</v>
       </c>
       <c r="E15" s="7">
-        <v>46.75</v>
-      </c>
-      <c r="F15" s="10">
-        <v>-1.1499999999999999</v>
-      </c>
-      <c r="G15" s="10">
-        <v>-2.37</v>
+        <v>44.85</v>
+      </c>
+      <c r="F15" s="8">
+        <v>-1.7</v>
+      </c>
+      <c r="G15" s="8">
+        <v>-3.59</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -1961,25 +1969,25 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>48.05</v>
+        <v>48.5</v>
       </c>
       <c r="C16" s="7">
-        <v>48.5</v>
+        <v>47.35</v>
       </c>
       <c r="D16" s="7">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="E16" s="7">
-        <v>46.85</v>
+        <v>46.75</v>
       </c>
       <c r="F16" s="8">
-        <v>0.45</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="G16" s="8">
-        <v>0.94</v>
+        <v>-2.37</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -2014,25 +2022,25 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
-        <v>48.15</v>
+        <v>48.05</v>
       </c>
       <c r="C17" s="7">
-        <v>48.05</v>
+        <v>48.5</v>
       </c>
       <c r="D17" s="7">
-        <v>64.5</v>
+        <v>53.5</v>
       </c>
       <c r="E17" s="7">
-        <v>47.05</v>
+        <v>46.85</v>
       </c>
       <c r="F17" s="10">
-        <v>-0.1</v>
+        <v>0.45</v>
       </c>
       <c r="G17" s="10">
-        <v>-0.21</v>
+        <v>0.94</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2067,25 +2075,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>42.1</v>
+        <v>48.15</v>
       </c>
       <c r="C18" s="7">
-        <v>48.15</v>
+        <v>48.05</v>
       </c>
       <c r="D18" s="7">
-        <v>51</v>
+        <v>64.5</v>
       </c>
       <c r="E18" s="7">
-        <v>39.700000000000003</v>
+        <v>47.05</v>
       </c>
       <c r="F18" s="8">
-        <v>6.05</v>
+        <v>-0.1</v>
       </c>
       <c r="G18" s="8">
-        <v>14.37</v>
+        <v>-0.21</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2120,25 +2128,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
-        <v>44.3</v>
+        <v>42.1</v>
       </c>
       <c r="C19" s="7">
-        <v>42.1</v>
+        <v>48.15</v>
       </c>
       <c r="D19" s="7">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="E19" s="7">
-        <v>37.85</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="F19" s="10">
-        <v>-2.2000000000000002</v>
+        <v>6.05</v>
       </c>
       <c r="G19" s="10">
-        <v>-4.97</v>
+        <v>14.37</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2173,25 +2181,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
-        <v>49.85</v>
+        <v>44.3</v>
       </c>
       <c r="C20" s="7">
-        <v>44.3</v>
+        <v>42.1</v>
       </c>
       <c r="D20" s="7">
-        <v>50.9</v>
+        <v>48.6</v>
       </c>
       <c r="E20" s="7">
-        <v>43.45</v>
-      </c>
-      <c r="F20" s="10">
-        <v>-5.55</v>
-      </c>
-      <c r="G20" s="10">
-        <v>-11.13</v>
+        <v>37.85</v>
+      </c>
+      <c r="F20" s="8">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="G20" s="8">
+        <v>-4.97</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2226,25 +2234,25 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>47.1</v>
+        <v>49.85</v>
       </c>
       <c r="C21" s="7">
-        <v>49.85</v>
+        <v>44.3</v>
       </c>
       <c r="D21" s="7">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="E21" s="7">
-        <v>45.5</v>
+        <v>43.45</v>
       </c>
       <c r="F21" s="8">
-        <v>2.75</v>
+        <v>-5.55</v>
       </c>
       <c r="G21" s="8">
-        <v>5.84</v>
+        <v>-11.13</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -2279,25 +2287,25 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>41</v>
+        <v>47.1</v>
       </c>
       <c r="C22" s="7">
-        <v>47.1</v>
+        <v>49.85</v>
       </c>
       <c r="D22" s="7">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="E22" s="7">
-        <v>40.5</v>
-      </c>
-      <c r="F22" s="8">
-        <v>6.1</v>
-      </c>
-      <c r="G22" s="8">
-        <v>14.88</v>
+        <v>45.5</v>
+      </c>
+      <c r="F22" s="10">
+        <v>2.75</v>
+      </c>
+      <c r="G22" s="10">
+        <v>5.84</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2332,25 +2340,25 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>45.55</v>
+        <v>41</v>
       </c>
       <c r="C23" s="7">
-        <v>41</v>
+        <v>47.1</v>
       </c>
       <c r="D23" s="7">
-        <v>47.45</v>
+        <v>51.1</v>
       </c>
       <c r="E23" s="7">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="F23" s="10">
-        <v>-4.55</v>
+        <v>6.1</v>
       </c>
       <c r="G23" s="10">
-        <v>-9.99</v>
+        <v>14.88</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
@@ -2385,25 +2393,25 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>46.05</v>
+        <v>45.55</v>
       </c>
       <c r="C24" s="7">
-        <v>45.55</v>
+        <v>41</v>
       </c>
       <c r="D24" s="7">
-        <v>49</v>
+        <v>47.45</v>
       </c>
       <c r="E24" s="7">
-        <v>39.450000000000003</v>
-      </c>
-      <c r="F24" s="10">
-        <v>-0.5</v>
-      </c>
-      <c r="G24" s="10">
-        <v>-1.0900000000000001</v>
+        <v>41</v>
+      </c>
+      <c r="F24" s="8">
+        <v>-4.55</v>
+      </c>
+      <c r="G24" s="8">
+        <v>-9.99</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2438,25 +2446,25 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>46.8</v>
+        <v>46.05</v>
       </c>
       <c r="C25" s="7">
-        <v>46.05</v>
+        <v>45.55</v>
       </c>
       <c r="D25" s="7">
-        <v>48.2</v>
+        <v>49</v>
       </c>
       <c r="E25" s="7">
-        <v>45.75</v>
-      </c>
-      <c r="F25" s="10">
-        <v>-0.75</v>
-      </c>
-      <c r="G25" s="10">
-        <v>-1.6</v>
+        <v>39.450000000000003</v>
+      </c>
+      <c r="F25" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="G25" s="8">
+        <v>-1.0900000000000001</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2491,25 +2499,25 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>46.15</v>
+        <v>46.8</v>
       </c>
       <c r="C26" s="7">
-        <v>46.8</v>
+        <v>46.05</v>
       </c>
       <c r="D26" s="7">
-        <v>50.6</v>
+        <v>48.2</v>
       </c>
       <c r="E26" s="7">
-        <v>45.8</v>
+        <v>45.75</v>
       </c>
       <c r="F26" s="8">
-        <v>0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="G26" s="8">
-        <v>1.41</v>
+        <v>-1.6</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2544,25 +2552,25 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>50.1</v>
+        <v>46.15</v>
       </c>
       <c r="C27" s="7">
-        <v>46.15</v>
+        <v>46.8</v>
       </c>
       <c r="D27" s="7">
-        <v>54.2</v>
+        <v>50.6</v>
       </c>
       <c r="E27" s="7">
-        <v>45.4</v>
+        <v>45.8</v>
       </c>
       <c r="F27" s="10">
-        <v>-3.95</v>
+        <v>0.65</v>
       </c>
       <c r="G27" s="10">
-        <v>-7.88</v>
+        <v>1.41</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2597,25 +2605,25 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>51.4</v>
+        <v>50.1</v>
       </c>
       <c r="C28" s="7">
-        <v>50.1</v>
+        <v>46.15</v>
       </c>
       <c r="D28" s="7">
-        <v>53.7</v>
+        <v>54.2</v>
       </c>
       <c r="E28" s="7">
-        <v>44.6</v>
-      </c>
-      <c r="F28" s="10">
-        <v>-1.3</v>
-      </c>
-      <c r="G28" s="10">
-        <v>-2.5299999999999998</v>
+        <v>45.4</v>
+      </c>
+      <c r="F28" s="8">
+        <v>-3.95</v>
+      </c>
+      <c r="G28" s="8">
+        <v>-7.88</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2650,25 +2658,25 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>42.6</v>
+        <v>51.4</v>
       </c>
       <c r="C29" s="7">
-        <v>51.4</v>
+        <v>50.1</v>
       </c>
       <c r="D29" s="7">
-        <v>62.2</v>
+        <v>53.7</v>
       </c>
       <c r="E29" s="7">
-        <v>42</v>
+        <v>44.6</v>
       </c>
       <c r="F29" s="8">
-        <v>8.8000000000000007</v>
+        <v>-1.3</v>
       </c>
       <c r="G29" s="8">
-        <v>20.66</v>
+        <v>-2.5299999999999998</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2703,25 +2711,25 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>38.65</v>
+        <v>42.6</v>
       </c>
       <c r="C30" s="7">
-        <v>42.6</v>
+        <v>51.4</v>
       </c>
       <c r="D30" s="7">
-        <v>46.2</v>
+        <v>62.2</v>
       </c>
       <c r="E30" s="7">
-        <v>35.5</v>
-      </c>
-      <c r="F30" s="8">
-        <v>3.95</v>
-      </c>
-      <c r="G30" s="8">
-        <v>10.220000000000001</v>
+        <v>42</v>
+      </c>
+      <c r="F30" s="10">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G30" s="10">
+        <v>20.66</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2756,25 +2764,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
-        <v>32.700000000000003</v>
+        <v>38.65</v>
       </c>
       <c r="C31" s="7">
-        <v>38.65</v>
+        <v>42.6</v>
       </c>
       <c r="D31" s="7">
-        <v>43.7</v>
+        <v>46.2</v>
       </c>
       <c r="E31" s="7">
-        <v>31.8</v>
-      </c>
-      <c r="F31" s="8">
-        <v>5.95</v>
-      </c>
-      <c r="G31" s="8">
-        <v>18.2</v>
+        <v>35.5</v>
+      </c>
+      <c r="F31" s="10">
+        <v>3.95</v>
+      </c>
+      <c r="G31" s="10">
+        <v>10.220000000000001</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2809,25 +2817,25 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>27.1</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="C32" s="7">
-        <v>32.700000000000003</v>
+        <v>38.65</v>
       </c>
       <c r="D32" s="7">
-        <v>36.450000000000003</v>
+        <v>43.7</v>
       </c>
       <c r="E32" s="7">
-        <v>27</v>
-      </c>
-      <c r="F32" s="8">
-        <v>5.6</v>
-      </c>
-      <c r="G32" s="8">
-        <v>20.66</v>
+        <v>31.8</v>
+      </c>
+      <c r="F32" s="10">
+        <v>5.95</v>
+      </c>
+      <c r="G32" s="10">
+        <v>18.2</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2862,25 +2870,25 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>46.5</v>
+        <v>27.1</v>
       </c>
       <c r="C33" s="7">
-        <v>27.1</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="D33" s="7">
-        <v>47</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="E33" s="7">
-        <v>20.88</v>
+        <v>27</v>
       </c>
       <c r="F33" s="10">
-        <v>-19.399999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="G33" s="10">
-        <v>-41.72</v>
+        <v>20.66</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2915,25 +2923,25 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>46.99</v>
+        <v>46.5</v>
       </c>
       <c r="C34" s="7">
-        <v>46.5</v>
+        <v>27.1</v>
       </c>
       <c r="D34" s="7">
-        <v>50.9</v>
+        <v>47</v>
       </c>
       <c r="E34" s="7">
-        <v>44.87</v>
-      </c>
-      <c r="F34" s="10">
-        <v>-0.49</v>
-      </c>
-      <c r="G34" s="10">
-        <v>-1.04</v>
+        <v>20.88</v>
+      </c>
+      <c r="F34" s="8">
+        <v>-19.399999999999999</v>
+      </c>
+      <c r="G34" s="8">
+        <v>-41.72</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2968,25 +2976,25 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>46.8</v>
+        <v>46.99</v>
       </c>
       <c r="C35" s="7">
-        <v>46.99</v>
+        <v>46.5</v>
       </c>
       <c r="D35" s="7">
-        <v>50.49</v>
+        <v>50.9</v>
       </c>
       <c r="E35" s="7">
-        <v>43.86</v>
+        <v>44.87</v>
       </c>
       <c r="F35" s="8">
-        <v>0.19</v>
+        <v>-0.49</v>
       </c>
       <c r="G35" s="8">
-        <v>0.41</v>
+        <v>-1.04</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3021,25 +3029,25 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7">
-        <v>47.45</v>
+        <v>46.8</v>
       </c>
       <c r="C36" s="7">
-        <v>46.8</v>
+        <v>46.99</v>
       </c>
       <c r="D36" s="7">
-        <v>48.49</v>
+        <v>50.49</v>
       </c>
       <c r="E36" s="7">
-        <v>45.61</v>
+        <v>43.86</v>
       </c>
       <c r="F36" s="10">
-        <v>-0.65</v>
+        <v>0.19</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.37</v>
+        <v>0.41</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3074,25 +3082,25 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7">
-        <v>51.31</v>
+        <v>47.45</v>
       </c>
       <c r="C37" s="7">
-        <v>47.45</v>
+        <v>46.8</v>
       </c>
       <c r="D37" s="7">
-        <v>52.19</v>
+        <v>48.49</v>
       </c>
       <c r="E37" s="7">
-        <v>46.55</v>
-      </c>
-      <c r="F37" s="10">
-        <v>-3.86</v>
-      </c>
-      <c r="G37" s="10">
-        <v>-7.52</v>
+        <v>45.61</v>
+      </c>
+      <c r="F37" s="8">
+        <v>-0.65</v>
+      </c>
+      <c r="G37" s="8">
+        <v>-1.37</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3127,25 +3135,25 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7">
-        <v>54.39</v>
+        <v>51.31</v>
       </c>
       <c r="C38" s="7">
-        <v>51.31</v>
+        <v>47.45</v>
       </c>
       <c r="D38" s="7">
-        <v>60.79</v>
+        <v>52.19</v>
       </c>
       <c r="E38" s="7">
-        <v>49.81</v>
-      </c>
-      <c r="F38" s="10">
-        <v>-3.08</v>
-      </c>
-      <c r="G38" s="10">
-        <v>-5.66</v>
+        <v>46.55</v>
+      </c>
+      <c r="F38" s="8">
+        <v>-3.86</v>
+      </c>
+      <c r="G38" s="8">
+        <v>-7.52</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3180,25 +3188,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7">
-        <v>49.42</v>
+        <v>54.39</v>
       </c>
       <c r="C39" s="7">
-        <v>54.39</v>
+        <v>51.31</v>
       </c>
       <c r="D39" s="7">
-        <v>54.99</v>
+        <v>60.79</v>
       </c>
       <c r="E39" s="7">
-        <v>49.61</v>
+        <v>49.81</v>
       </c>
       <c r="F39" s="8">
-        <v>4.97</v>
+        <v>-3.08</v>
       </c>
       <c r="G39" s="8">
-        <v>10.06</v>
+        <v>-5.66</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3233,25 +3241,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7">
-        <v>49.19</v>
+        <v>49.42</v>
       </c>
       <c r="C40" s="7">
-        <v>49.42</v>
+        <v>54.39</v>
       </c>
       <c r="D40" s="7">
-        <v>52.17</v>
+        <v>54.99</v>
       </c>
       <c r="E40" s="7">
-        <v>45.38</v>
-      </c>
-      <c r="F40" s="8">
-        <v>0.23</v>
-      </c>
-      <c r="G40" s="8">
-        <v>0.47</v>
+        <v>49.61</v>
+      </c>
+      <c r="F40" s="10">
+        <v>4.97</v>
+      </c>
+      <c r="G40" s="10">
+        <v>10.06</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3286,25 +3294,25 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7">
-        <v>51.9</v>
+        <v>49.19</v>
       </c>
       <c r="C41" s="7">
-        <v>49.19</v>
+        <v>49.42</v>
       </c>
       <c r="D41" s="7">
-        <v>54.73</v>
+        <v>52.17</v>
       </c>
       <c r="E41" s="7">
-        <v>48.51</v>
+        <v>45.38</v>
       </c>
       <c r="F41" s="10">
-        <v>-2.71</v>
+        <v>0.23</v>
       </c>
       <c r="G41" s="10">
-        <v>-5.22</v>
+        <v>0.47</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
@@ -3339,25 +3347,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7">
-        <v>44.74</v>
+        <v>51.9</v>
       </c>
       <c r="C42" s="7">
-        <v>51.9</v>
+        <v>49.19</v>
       </c>
       <c r="D42" s="7">
-        <v>54.9</v>
+        <v>54.73</v>
       </c>
       <c r="E42" s="7">
-        <v>44.21</v>
+        <v>48.51</v>
       </c>
       <c r="F42" s="8">
-        <v>7.16</v>
+        <v>-2.71</v>
       </c>
       <c r="G42" s="8">
-        <v>16</v>
+        <v>-5.22</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3392,25 +3400,25 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7">
-        <v>50.35</v>
+        <v>44.74</v>
       </c>
       <c r="C43" s="7">
-        <v>44.74</v>
+        <v>51.9</v>
       </c>
       <c r="D43" s="7">
-        <v>50.99</v>
+        <v>54.9</v>
       </c>
       <c r="E43" s="7">
-        <v>43.4</v>
+        <v>44.21</v>
       </c>
       <c r="F43" s="10">
-        <v>-5.61</v>
+        <v>7.16</v>
       </c>
       <c r="G43" s="10">
-        <v>-11.14</v>
+        <v>16</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
@@ -3445,25 +3453,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7">
-        <v>52.62</v>
+        <v>50.35</v>
       </c>
       <c r="C44" s="7">
-        <v>50.35</v>
+        <v>44.74</v>
       </c>
       <c r="D44" s="7">
-        <v>53.2</v>
+        <v>50.99</v>
       </c>
       <c r="E44" s="7">
-        <v>49.81</v>
-      </c>
-      <c r="F44" s="10">
-        <v>-2.27</v>
-      </c>
-      <c r="G44" s="10">
-        <v>-4.3099999999999996</v>
+        <v>43.4</v>
+      </c>
+      <c r="F44" s="8">
+        <v>-5.61</v>
+      </c>
+      <c r="G44" s="8">
+        <v>-11.14</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3498,25 +3506,25 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7">
-        <v>59.49</v>
+        <v>52.62</v>
       </c>
       <c r="C45" s="7">
-        <v>52.62</v>
+        <v>50.35</v>
       </c>
       <c r="D45" s="7">
-        <v>59.5</v>
+        <v>53.2</v>
       </c>
       <c r="E45" s="7">
-        <v>52.5</v>
-      </c>
-      <c r="F45" s="10">
-        <v>-6.87</v>
-      </c>
-      <c r="G45" s="10">
-        <v>-11.55</v>
+        <v>49.81</v>
+      </c>
+      <c r="F45" s="8">
+        <v>-2.27</v>
+      </c>
+      <c r="G45" s="8">
+        <v>-4.3099999999999996</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -3551,25 +3559,25 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7">
-        <v>57</v>
+        <v>59.49</v>
       </c>
       <c r="C46" s="7">
-        <v>59.49</v>
+        <v>52.62</v>
       </c>
       <c r="D46" s="7">
-        <v>61.99</v>
+        <v>59.5</v>
       </c>
       <c r="E46" s="7">
-        <v>50.91</v>
+        <v>52.5</v>
       </c>
       <c r="F46" s="8">
-        <v>2.4900000000000002</v>
+        <v>-6.87</v>
       </c>
       <c r="G46" s="8">
-        <v>4.37</v>
+        <v>-11.55</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3604,25 +3612,25 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7">
-        <v>54.17</v>
+        <v>57</v>
       </c>
       <c r="C47" s="7">
-        <v>57</v>
+        <v>59.49</v>
       </c>
       <c r="D47" s="7">
-        <v>63.49</v>
+        <v>61.99</v>
       </c>
       <c r="E47" s="7">
-        <v>54.5</v>
-      </c>
-      <c r="F47" s="8">
-        <v>2.83</v>
-      </c>
-      <c r="G47" s="8">
-        <v>5.22</v>
+        <v>50.91</v>
+      </c>
+      <c r="F47" s="10">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="G47" s="10">
+        <v>4.37</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
@@ -3657,25 +3665,25 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7">
-        <v>60.99</v>
+        <v>54.17</v>
       </c>
       <c r="C48" s="7">
-        <v>54.17</v>
+        <v>57</v>
       </c>
       <c r="D48" s="7">
-        <v>61.99</v>
+        <v>63.49</v>
       </c>
       <c r="E48" s="7">
-        <v>52</v>
+        <v>54.5</v>
       </c>
       <c r="F48" s="10">
-        <v>-6.82</v>
+        <v>2.83</v>
       </c>
       <c r="G48" s="10">
-        <v>-11.18</v>
+        <v>5.22</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -3710,25 +3718,25 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7">
-        <v>51.2</v>
+        <v>60.99</v>
       </c>
       <c r="C49" s="7">
-        <v>60.99</v>
+        <v>54.17</v>
       </c>
       <c r="D49" s="7">
-        <v>67</v>
+        <v>61.99</v>
       </c>
       <c r="E49" s="7">
-        <v>49.81</v>
+        <v>52</v>
       </c>
       <c r="F49" s="8">
-        <v>9.7899999999999991</v>
+        <v>-6.82</v>
       </c>
       <c r="G49" s="8">
-        <v>19.12</v>
+        <v>-11.18</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -3763,25 +3771,25 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7">
-        <v>64</v>
+        <v>51.2</v>
       </c>
       <c r="C50" s="7">
-        <v>51.2</v>
+        <v>60.99</v>
       </c>
       <c r="D50" s="7">
-        <v>70.489999999999995</v>
+        <v>67</v>
       </c>
       <c r="E50" s="7">
-        <v>50.19</v>
+        <v>49.81</v>
       </c>
       <c r="F50" s="10">
-        <v>-12.8</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="G50" s="10">
-        <v>-20</v>
+        <v>19.12</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3816,25 +3824,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7">
-        <v>69.709999999999994</v>
+        <v>64</v>
       </c>
       <c r="C51" s="7">
-        <v>64</v>
+        <v>51.2</v>
       </c>
       <c r="D51" s="7">
-        <v>70.209999999999994</v>
+        <v>70.489999999999995</v>
       </c>
       <c r="E51" s="7">
-        <v>59.53</v>
-      </c>
-      <c r="F51" s="10">
-        <v>-5.71</v>
-      </c>
-      <c r="G51" s="10">
-        <v>-8.19</v>
+        <v>50.19</v>
+      </c>
+      <c r="F51" s="8">
+        <v>-12.8</v>
+      </c>
+      <c r="G51" s="8">
+        <v>-20</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3869,25 +3877,25 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7">
-        <v>85.5</v>
+        <v>69.709999999999994</v>
       </c>
       <c r="C52" s="7">
-        <v>69.709999999999994</v>
+        <v>64</v>
       </c>
       <c r="D52" s="7">
-        <v>85</v>
+        <v>70.209999999999994</v>
       </c>
       <c r="E52" s="7">
-        <v>69.61</v>
-      </c>
-      <c r="F52" s="10">
-        <v>-15.79</v>
-      </c>
-      <c r="G52" s="10">
-        <v>-18.47</v>
+        <v>59.53</v>
+      </c>
+      <c r="F52" s="8">
+        <v>-5.71</v>
+      </c>
+      <c r="G52" s="8">
+        <v>-8.19</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
@@ -3922,25 +3930,25 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7">
-        <v>90.8</v>
+        <v>85.5</v>
       </c>
       <c r="C53" s="7">
-        <v>85.5</v>
+        <v>69.709999999999994</v>
       </c>
       <c r="D53" s="7">
-        <v>93.5</v>
+        <v>85</v>
       </c>
       <c r="E53" s="7">
-        <v>85</v>
-      </c>
-      <c r="F53" s="10">
-        <v>-5.3</v>
-      </c>
-      <c r="G53" s="10">
-        <v>-5.84</v>
+        <v>69.61</v>
+      </c>
+      <c r="F53" s="8">
+        <v>-15.79</v>
+      </c>
+      <c r="G53" s="8">
+        <v>-18.47</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -3975,25 +3983,25 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7">
-        <v>82.1</v>
+        <v>90.8</v>
       </c>
       <c r="C54" s="7">
-        <v>90.8</v>
+        <v>85.5</v>
       </c>
       <c r="D54" s="7">
-        <v>104</v>
+        <v>93.5</v>
       </c>
       <c r="E54" s="7">
-        <v>82.5</v>
+        <v>85</v>
       </c>
       <c r="F54" s="8">
-        <v>8.6999999999999993</v>
+        <v>-5.3</v>
       </c>
       <c r="G54" s="8">
-        <v>10.6</v>
+        <v>-5.84</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
@@ -4028,25 +4036,25 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7">
-        <v>71.989999999999995</v>
+        <v>82.1</v>
       </c>
       <c r="C55" s="7">
-        <v>82.1</v>
+        <v>90.8</v>
       </c>
       <c r="D55" s="7">
-        <v>85.29</v>
+        <v>104</v>
       </c>
       <c r="E55" s="7">
-        <v>65</v>
-      </c>
-      <c r="F55" s="8">
-        <v>10.11</v>
-      </c>
-      <c r="G55" s="8">
-        <v>14.04</v>
+        <v>82.5</v>
+      </c>
+      <c r="F55" s="10">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G55" s="10">
+        <v>10.6</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -4081,25 +4089,25 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7">
-        <v>73.099999999999994</v>
+        <v>71.989999999999995</v>
       </c>
       <c r="C56" s="7">
-        <v>71.989999999999995</v>
+        <v>82.1</v>
       </c>
       <c r="D56" s="7">
-        <v>82.99</v>
+        <v>85.29</v>
       </c>
       <c r="E56" s="7">
-        <v>70.260000000000005</v>
+        <v>65</v>
       </c>
       <c r="F56" s="10">
-        <v>-1.1100000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="G56" s="10">
-        <v>-1.52</v>
+        <v>14.04</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -4134,25 +4142,25 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7">
-        <v>55.7</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="C57" s="7">
-        <v>73.099999999999994</v>
+        <v>71.989999999999995</v>
       </c>
       <c r="D57" s="7">
-        <v>76</v>
+        <v>82.99</v>
       </c>
       <c r="E57" s="7">
-        <v>53</v>
+        <v>70.260000000000005</v>
       </c>
       <c r="F57" s="8">
-        <v>17.399999999999999</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="G57" s="8">
-        <v>31.24</v>
+        <v>-1.52</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -4187,25 +4195,25 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7">
-        <v>50</v>
+        <v>55.7</v>
       </c>
       <c r="C58" s="7">
-        <v>55.7</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="D58" s="7">
-        <v>60.99</v>
+        <v>76</v>
       </c>
       <c r="E58" s="7">
-        <v>47.51</v>
-      </c>
-      <c r="F58" s="8">
-        <v>5.7</v>
-      </c>
-      <c r="G58" s="8">
-        <v>11.4</v>
+        <v>53</v>
+      </c>
+      <c r="F58" s="10">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G58" s="10">
+        <v>31.24</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4240,25 +4248,25 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7">
-        <v>51.56</v>
+        <v>50</v>
       </c>
       <c r="C59" s="7">
-        <v>50</v>
+        <v>55.7</v>
       </c>
       <c r="D59" s="7">
-        <v>56.49</v>
+        <v>60.99</v>
       </c>
       <c r="E59" s="7">
-        <v>45.61</v>
+        <v>47.51</v>
       </c>
       <c r="F59" s="10">
-        <v>-1.56</v>
+        <v>5.7</v>
       </c>
       <c r="G59" s="10">
-        <v>-3.03</v>
+        <v>11.4</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
@@ -4293,25 +4301,25 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7">
-        <v>52.49</v>
+        <v>51.56</v>
       </c>
       <c r="C60" s="7">
-        <v>51.56</v>
+        <v>50</v>
       </c>
       <c r="D60" s="7">
-        <v>56.99</v>
+        <v>56.49</v>
       </c>
       <c r="E60" s="7">
-        <v>45.9</v>
-      </c>
-      <c r="F60" s="10">
-        <v>-0.93</v>
-      </c>
-      <c r="G60" s="10">
-        <v>-1.77</v>
+        <v>45.61</v>
+      </c>
+      <c r="F60" s="8">
+        <v>-1.56</v>
+      </c>
+      <c r="G60" s="8">
+        <v>-3.03</v>
       </c>
       <c r="H60" s="9">
         <v>0</v>
@@ -4346,25 +4354,25 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7">
-        <v>62.2</v>
+        <v>52.49</v>
       </c>
       <c r="C61" s="7">
-        <v>52.49</v>
+        <v>51.56</v>
       </c>
       <c r="D61" s="7">
-        <v>63.99</v>
+        <v>56.99</v>
       </c>
       <c r="E61" s="7">
-        <v>49.85</v>
-      </c>
-      <c r="F61" s="10">
-        <v>-9.7100000000000009</v>
-      </c>
-      <c r="G61" s="10">
-        <v>-15.61</v>
+        <v>45.9</v>
+      </c>
+      <c r="F61" s="8">
+        <v>-0.93</v>
+      </c>
+      <c r="G61" s="8">
+        <v>-1.77</v>
       </c>
       <c r="H61" s="9">
         <v>0</v>
@@ -4399,25 +4407,25 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7">
-        <v>68.989999999999995</v>
+        <v>62.2</v>
       </c>
       <c r="C62" s="7">
-        <v>62.2</v>
+        <v>52.49</v>
       </c>
       <c r="D62" s="7">
-        <v>69.489999999999995</v>
+        <v>63.99</v>
       </c>
       <c r="E62" s="7">
-        <v>60.01</v>
-      </c>
-      <c r="F62" s="10">
-        <v>-6.79</v>
-      </c>
-      <c r="G62" s="10">
-        <v>-9.84</v>
+        <v>49.85</v>
+      </c>
+      <c r="F62" s="8">
+        <v>-9.7100000000000009</v>
+      </c>
+      <c r="G62" s="8">
+        <v>-15.61</v>
       </c>
       <c r="H62" s="9">
         <v>0</v>
@@ -4452,25 +4460,25 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B63" s="7">
-        <v>77.73</v>
+        <v>68.989999999999995</v>
       </c>
       <c r="C63" s="7">
-        <v>68.989999999999995</v>
+        <v>62.2</v>
       </c>
       <c r="D63" s="7">
-        <v>81.680000000000007</v>
+        <v>69.489999999999995</v>
       </c>
       <c r="E63" s="7">
-        <v>61.86</v>
-      </c>
-      <c r="F63" s="10">
-        <v>-8.74</v>
-      </c>
-      <c r="G63" s="10">
-        <v>-11.24</v>
+        <v>60.01</v>
+      </c>
+      <c r="F63" s="8">
+        <v>-6.79</v>
+      </c>
+      <c r="G63" s="8">
+        <v>-9.84</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -4505,25 +4513,25 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7">
-        <v>80.77</v>
+        <v>77.73</v>
       </c>
       <c r="C64" s="7">
-        <v>77.73</v>
+        <v>68.989999999999995</v>
       </c>
       <c r="D64" s="7">
-        <v>81.709999999999994</v>
+        <v>81.680000000000007</v>
       </c>
       <c r="E64" s="7">
-        <v>73.98</v>
-      </c>
-      <c r="F64" s="10">
-        <v>-3.04</v>
-      </c>
-      <c r="G64" s="10">
-        <v>-3.76</v>
+        <v>61.86</v>
+      </c>
+      <c r="F64" s="8">
+        <v>-8.74</v>
+      </c>
+      <c r="G64" s="8">
+        <v>-11.24</v>
       </c>
       <c r="H64" s="9">
         <v>0</v>
@@ -4558,25 +4566,25 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7">
-        <v>80.8</v>
+        <v>80.77</v>
       </c>
       <c r="C65" s="7">
-        <v>80.77</v>
+        <v>77.73</v>
       </c>
       <c r="D65" s="7">
-        <v>86.83</v>
+        <v>81.709999999999994</v>
       </c>
       <c r="E65" s="7">
-        <v>78.010000000000005</v>
-      </c>
-      <c r="F65" s="10">
-        <v>-0.03</v>
-      </c>
-      <c r="G65" s="10">
-        <v>-0.04</v>
+        <v>73.98</v>
+      </c>
+      <c r="F65" s="8">
+        <v>-3.04</v>
+      </c>
+      <c r="G65" s="8">
+        <v>-3.76</v>
       </c>
       <c r="H65" s="9">
         <v>0</v>
@@ -4611,25 +4619,25 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7">
-        <v>80.25</v>
+        <v>80.8</v>
       </c>
       <c r="C66" s="7">
-        <v>80.8</v>
+        <v>80.77</v>
       </c>
       <c r="D66" s="7">
-        <v>88.67</v>
+        <v>86.83</v>
       </c>
       <c r="E66" s="7">
-        <v>77.010000000000005</v>
+        <v>78.010000000000005</v>
       </c>
       <c r="F66" s="8">
-        <v>0.55000000000000004</v>
+        <v>-0.03</v>
       </c>
       <c r="G66" s="8">
-        <v>0.69</v>
+        <v>-0.04</v>
       </c>
       <c r="H66" s="9">
         <v>0</v>
@@ -4664,25 +4672,25 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B67" s="7">
-        <v>72.5</v>
+        <v>80.25</v>
       </c>
       <c r="C67" s="7">
-        <v>80.25</v>
+        <v>80.8</v>
       </c>
       <c r="D67" s="7">
-        <v>90.52</v>
+        <v>88.67</v>
       </c>
       <c r="E67" s="7">
-        <v>71.59</v>
-      </c>
-      <c r="F67" s="8">
-        <v>7.75</v>
-      </c>
-      <c r="G67" s="8">
-        <v>10.69</v>
+        <v>77.010000000000005</v>
+      </c>
+      <c r="F67" s="10">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G67" s="10">
+        <v>0.69</v>
       </c>
       <c r="H67" s="9">
         <v>0</v>
@@ -4717,25 +4725,25 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B68" s="7">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="C68" s="7">
-        <v>72.5</v>
+        <v>80.25</v>
       </c>
       <c r="D68" s="7">
-        <v>75.8</v>
+        <v>90.52</v>
       </c>
       <c r="E68" s="7">
-        <v>71.319999999999993</v>
+        <v>71.59</v>
       </c>
       <c r="F68" s="10">
-        <v>-1</v>
+        <v>7.75</v>
       </c>
       <c r="G68" s="10">
-        <v>-1.36</v>
+        <v>10.69</v>
       </c>
       <c r="H68" s="9">
         <v>0</v>
@@ -4770,25 +4778,25 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B69" s="7">
-        <v>83.5</v>
+        <v>73.5</v>
       </c>
       <c r="C69" s="7">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="D69" s="7">
-        <v>84.9</v>
+        <v>75.8</v>
       </c>
       <c r="E69" s="7">
-        <v>72.3</v>
-      </c>
-      <c r="F69" s="10">
-        <v>-10</v>
-      </c>
-      <c r="G69" s="10">
-        <v>-11.98</v>
+        <v>71.319999999999993</v>
+      </c>
+      <c r="F69" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G69" s="8">
+        <v>-1.36</v>
       </c>
       <c r="H69" s="9">
         <v>0</v>
@@ -4823,25 +4831,25 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B70" s="7">
-        <v>88.65</v>
+        <v>83.5</v>
       </c>
       <c r="C70" s="7">
-        <v>83.5</v>
+        <v>73.5</v>
       </c>
       <c r="D70" s="7">
-        <v>91.5</v>
+        <v>84.9</v>
       </c>
       <c r="E70" s="7">
-        <v>70.010000000000005</v>
-      </c>
-      <c r="F70" s="10">
-        <v>-5.15</v>
-      </c>
-      <c r="G70" s="10">
-        <v>-5.81</v>
+        <v>72.3</v>
+      </c>
+      <c r="F70" s="8">
+        <v>-10</v>
+      </c>
+      <c r="G70" s="8">
+        <v>-11.98</v>
       </c>
       <c r="H70" s="9">
         <v>0</v>
@@ -4876,25 +4884,25 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B71" s="7">
-        <v>104</v>
+        <v>88.65</v>
       </c>
       <c r="C71" s="7">
-        <v>88.65</v>
+        <v>83.5</v>
       </c>
       <c r="D71" s="7">
-        <v>104</v>
+        <v>91.5</v>
       </c>
       <c r="E71" s="7">
-        <v>86.49</v>
-      </c>
-      <c r="F71" s="10">
-        <v>-15.35</v>
-      </c>
-      <c r="G71" s="10">
-        <v>-14.76</v>
+        <v>70.010000000000005</v>
+      </c>
+      <c r="F71" s="8">
+        <v>-5.15</v>
+      </c>
+      <c r="G71" s="8">
+        <v>-5.81</v>
       </c>
       <c r="H71" s="9">
         <v>0</v>
@@ -4929,25 +4937,25 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B72" s="7">
-        <v>102.3</v>
+        <v>104</v>
       </c>
       <c r="C72" s="7">
+        <v>88.65</v>
+      </c>
+      <c r="D72" s="7">
         <v>104</v>
       </c>
-      <c r="D72" s="7">
-        <v>108</v>
-      </c>
       <c r="E72" s="7">
-        <v>97.51</v>
+        <v>86.49</v>
       </c>
       <c r="F72" s="8">
-        <v>1.7</v>
+        <v>-15.35</v>
       </c>
       <c r="G72" s="8">
-        <v>1.66</v>
+        <v>-14.76</v>
       </c>
       <c r="H72" s="9">
         <v>0</v>
@@ -4982,25 +4990,25 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B73" s="7">
-        <v>113</v>
+        <v>102.3</v>
       </c>
       <c r="C73" s="7">
-        <v>102.3</v>
+        <v>104</v>
       </c>
       <c r="D73" s="7">
-        <v>113.34</v>
+        <v>108</v>
       </c>
       <c r="E73" s="7">
-        <v>99</v>
+        <v>97.51</v>
       </c>
       <c r="F73" s="10">
-        <v>-10.7</v>
+        <v>1.7</v>
       </c>
       <c r="G73" s="10">
-        <v>-9.4700000000000006</v>
+        <v>1.66</v>
       </c>
       <c r="H73" s="9">
         <v>0</v>
@@ -5035,25 +5043,25 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B74" s="7">
-        <v>126.32</v>
+        <v>113</v>
       </c>
       <c r="C74" s="7">
-        <v>113</v>
+        <v>102.3</v>
       </c>
       <c r="D74" s="7">
-        <v>128.4</v>
+        <v>113.34</v>
       </c>
       <c r="E74" s="7">
-        <v>111.02</v>
-      </c>
-      <c r="F74" s="10">
-        <v>-13.32</v>
-      </c>
-      <c r="G74" s="10">
-        <v>-10.54</v>
+        <v>99</v>
+      </c>
+      <c r="F74" s="8">
+        <v>-10.7</v>
+      </c>
+      <c r="G74" s="8">
+        <v>-9.4700000000000006</v>
       </c>
       <c r="H74" s="9">
         <v>0</v>
@@ -5088,25 +5096,25 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B75" s="7">
-        <v>119</v>
+        <v>126.32</v>
       </c>
       <c r="C75" s="7">
-        <v>126.32</v>
+        <v>113</v>
       </c>
       <c r="D75" s="7">
-        <v>132.63</v>
+        <v>128.4</v>
       </c>
       <c r="E75" s="7">
-        <v>118</v>
+        <v>111.02</v>
       </c>
       <c r="F75" s="8">
-        <v>7.32</v>
+        <v>-13.32</v>
       </c>
       <c r="G75" s="8">
-        <v>6.15</v>
+        <v>-10.54</v>
       </c>
       <c r="H75" s="9">
         <v>0</v>
@@ -5141,25 +5149,25 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B76" s="7">
-        <v>136.31</v>
+        <v>119</v>
       </c>
       <c r="C76" s="7">
-        <v>119</v>
+        <v>126.32</v>
       </c>
       <c r="D76" s="7">
-        <v>139.63999999999999</v>
+        <v>132.63</v>
       </c>
       <c r="E76" s="7">
-        <v>117.7</v>
+        <v>118</v>
       </c>
       <c r="F76" s="10">
-        <v>-17.309999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="G76" s="10">
-        <v>-12.7</v>
+        <v>6.15</v>
       </c>
       <c r="H76" s="9">
         <v>0</v>
@@ -5194,25 +5202,25 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B77" s="7">
-        <v>139.34</v>
+        <v>136.31</v>
       </c>
       <c r="C77" s="7">
-        <v>136.31</v>
+        <v>119</v>
       </c>
       <c r="D77" s="7">
-        <v>154.71</v>
+        <v>139.63999999999999</v>
       </c>
       <c r="E77" s="7">
-        <v>136.16999999999999</v>
-      </c>
-      <c r="F77" s="10">
-        <v>-3.03</v>
-      </c>
-      <c r="G77" s="10">
-        <v>-2.17</v>
+        <v>117.7</v>
+      </c>
+      <c r="F77" s="8">
+        <v>-17.309999999999999</v>
+      </c>
+      <c r="G77" s="8">
+        <v>-12.7</v>
       </c>
       <c r="H77" s="9">
         <v>0</v>
@@ -5247,25 +5255,25 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B78" s="7">
-        <v>119.79</v>
+        <v>139.34</v>
       </c>
       <c r="C78" s="7">
-        <v>139.34</v>
+        <v>136.31</v>
       </c>
       <c r="D78" s="7">
-        <v>156.30000000000001</v>
+        <v>154.71</v>
       </c>
       <c r="E78" s="7">
-        <v>110.01</v>
+        <v>136.16999999999999</v>
       </c>
       <c r="F78" s="8">
-        <v>19.55</v>
+        <v>-3.03</v>
       </c>
       <c r="G78" s="8">
-        <v>16.32</v>
+        <v>-2.17</v>
       </c>
       <c r="H78" s="9">
         <v>0</v>
@@ -5300,25 +5308,25 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B79" s="7">
-        <v>120.87</v>
+        <v>119.79</v>
       </c>
       <c r="C79" s="7">
-        <v>119.79</v>
+        <v>139.34</v>
       </c>
       <c r="D79" s="7">
-        <v>128.99</v>
+        <v>156.30000000000001</v>
       </c>
       <c r="E79" s="7">
-        <v>98.03</v>
+        <v>110.01</v>
       </c>
       <c r="F79" s="10">
-        <v>-1.08</v>
+        <v>19.55</v>
       </c>
       <c r="G79" s="10">
-        <v>-0.89</v>
+        <v>16.32</v>
       </c>
       <c r="H79" s="9">
         <v>0</v>
@@ -5353,25 +5361,25 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B80" s="7">
-        <v>139.99</v>
+        <v>120.87</v>
       </c>
       <c r="C80" s="7">
-        <v>120.87</v>
+        <v>119.79</v>
       </c>
       <c r="D80" s="7">
-        <v>147.35</v>
+        <v>128.99</v>
       </c>
       <c r="E80" s="7">
-        <v>116.86</v>
-      </c>
-      <c r="F80" s="10">
-        <v>-19.12</v>
-      </c>
-      <c r="G80" s="10">
-        <v>-13.66</v>
+        <v>98.03</v>
+      </c>
+      <c r="F80" s="8">
+        <v>-1.08</v>
+      </c>
+      <c r="G80" s="8">
+        <v>-0.89</v>
       </c>
       <c r="H80" s="9">
         <v>0</v>
@@ -5406,25 +5414,25 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B81" s="7">
-        <v>184</v>
+        <v>139.99</v>
       </c>
       <c r="C81" s="7">
-        <v>139.99</v>
+        <v>120.87</v>
       </c>
       <c r="D81" s="7">
-        <v>194.59</v>
+        <v>147.35</v>
       </c>
       <c r="E81" s="7">
-        <v>117.01</v>
-      </c>
-      <c r="F81" s="10">
-        <v>-44.01</v>
-      </c>
-      <c r="G81" s="10">
-        <v>-23.92</v>
+        <v>116.86</v>
+      </c>
+      <c r="F81" s="8">
+        <v>-19.12</v>
+      </c>
+      <c r="G81" s="8">
+        <v>-13.66</v>
       </c>
       <c r="H81" s="9">
         <v>0</v>
@@ -5459,25 +5467,25 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B82" s="7">
-        <v>249</v>
+        <v>184</v>
       </c>
       <c r="C82" s="7">
-        <v>184</v>
+        <v>139.99</v>
       </c>
       <c r="D82" s="7">
-        <v>251.99</v>
+        <v>194.59</v>
       </c>
       <c r="E82" s="7">
-        <v>168.01</v>
-      </c>
-      <c r="F82" s="10">
-        <v>-65</v>
-      </c>
-      <c r="G82" s="10">
-        <v>-26.1</v>
+        <v>117.01</v>
+      </c>
+      <c r="F82" s="8">
+        <v>-44.01</v>
+      </c>
+      <c r="G82" s="8">
+        <v>-23.92</v>
       </c>
       <c r="H82" s="9">
         <v>0</v>
@@ -5512,25 +5520,25 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B83" s="7">
-        <v>260.98</v>
+        <v>249</v>
       </c>
       <c r="C83" s="7">
-        <v>249</v>
+        <v>184</v>
       </c>
       <c r="D83" s="7">
-        <v>265</v>
+        <v>251.99</v>
       </c>
       <c r="E83" s="7">
-        <v>199</v>
-      </c>
-      <c r="F83" s="10">
-        <v>-12.98</v>
-      </c>
-      <c r="G83" s="10">
-        <v>-4.95</v>
+        <v>168.01</v>
+      </c>
+      <c r="F83" s="8">
+        <v>-65</v>
+      </c>
+      <c r="G83" s="8">
+        <v>-26.1</v>
       </c>
       <c r="H83" s="9">
         <v>0</v>
@@ -5565,54 +5573,107 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
+        <v>42370</v>
+      </c>
+      <c r="B84" s="7">
+        <v>260.98</v>
+      </c>
+      <c r="C84" s="7">
+        <v>249</v>
+      </c>
+      <c r="D84" s="7">
+        <v>265</v>
+      </c>
+      <c r="E84" s="7">
+        <v>199</v>
+      </c>
+      <c r="F84" s="8">
+        <v>-12.98</v>
+      </c>
+      <c r="G84" s="8">
+        <v>-4.95</v>
+      </c>
+      <c r="H84" s="9">
+        <v>0</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84" s="9">
+        <v>0</v>
+      </c>
+      <c r="L84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M84" s="9">
+        <v>0</v>
+      </c>
+      <c r="N84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
         <v>42339</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H84" s="9">
-        <v>0</v>
-      </c>
-      <c r="I84" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K84" s="9">
-        <v>0</v>
-      </c>
-      <c r="L84" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M84" s="9">
-        <v>0</v>
-      </c>
-      <c r="N84" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O84" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P84" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="9" t="s">
+      <c r="B85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H85" s="9">
+        <v>0</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85" s="9">
+        <v>0</v>
+      </c>
+      <c r="L85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M85" s="9">
+        <v>0</v>
+      </c>
+      <c r="N85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P85" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5631,7 +5692,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>